--- a/imageCreationExcel/Bright/Master/MASTER_2.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_2.xlsx
@@ -552,15 +552,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\0_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_2_1_R_filler_0_day_rain_empty_MODEL.jpg</t>
+          <t>M_2_1_R_filler_0_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -606,15 +624,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_2_2_1_match_1_day_sun_busy_MODEL.jpg</t>
+          <t>M_2_2_1_match_1_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -714,15 +750,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\8_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M_2_4_C_filler_8_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_4_C_filler_8_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +822,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_2_5_I_filler_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_5_I_filler_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -822,15 +882,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>M_2_6_4_unmatch_1_day_rain_busy_MODEL.jpg</t>
+          <t>M_2_6_4_unmatch_1_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1062,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_2_9_3_match_3_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_9_3_match_3_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1122,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\3_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_2_10_S_filler_3_day_rain_empty_MODEL.jpg</t>
+          <t>M_2_10_S_filler_3_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1092,15 +1194,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\4_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>M_2_11_I_filler_4_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_11_I_filler_4_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1362,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_2_14_F_filler_4_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_14_F_filler_4_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1308,15 +1422,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>M_2_15_2_unmatch_5_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_15_2_unmatch_5_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1416,15 +1548,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>M_2_17_D_filler_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_17_D_filler_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1470,15 +1620,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>M_2_18_L_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_2_18_L_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1746,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_2_20_Q_filler_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_20_Q_filler_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1860,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_2_22_4_unmatch_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_22_4_unmatch_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1974,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\8_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_2_24_8_match_8_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_24_8_match_8_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -1902,15 +2088,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>M_2_26_T_filler_3_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_26_T_filler_3_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2202,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_2_28_G_filler_1_day_rain_empty_MODEL.jpg</t>
+          <t>M_2_28_G_filler_1_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2064,15 +2274,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\4_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>M_2_29_Q_filler_4_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_29_Q_filler_4_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2334,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\6_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_2_30_6_match_6_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_30_6_match_6_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2226,15 +2448,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>M_2_32_2_match_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_32_2_match_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2280,15 +2520,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>M_2_33_P_filler_1_day_rain_busy_MODEL.jpg</t>
+          <t>M_2_33_P_filler_1_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2700,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_2_36_1_match_1_day_rain_busy_MODEL.jpg</t>
+          <t>M_2_36_1_match_1_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2496,15 +2772,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>M_2_37_U_filler_4_day_sun_busy_MODEL.jpg</t>
+          <t>M_2_37_U_filler_4_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2844,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_2_38_T_filler_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_38_T_filler_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2904,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\6_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_2_39_U_filler_6_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_39_U_filler_6_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2712,15 +3018,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\6_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>M_2_41_6_match_6_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_41_6_match_6_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,15 +3078,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\1_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>M_2_42_E_filler_1_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_42_E_filler_1_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3192,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_2_44_J_filler_7_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_44_J_filler_7_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3264,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_2_45_4_unmatch_5_day_rain_busy_MODEL.jpg</t>
+          <t>M_2_45_4_unmatch_5_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3336,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\1_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_2_46_I_filler_1_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_2_46_I_filler_1_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -3036,15 +3396,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\9_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>M_2_47_U_filler_9_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_2_47_U_filler_9_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3456,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_2_48_P_filler_2_day_sun_empty_MODEL.jpg</t>
+          <t>M_2_48_P_filler_2_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
